--- a/data/trans_orig/IP42-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP42-Estudios-trans_orig.xlsx
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43946</t>
+          <t>44717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54784</t>
+          <t>54858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>52472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62859</t>
+          <t>62963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99742</t>
+          <t>100799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115258</t>
+          <t>115465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18916</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>35495</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>55176</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>58418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77917</t>
+          <t>77766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105862</t>
+          <t>107177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41806</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64196</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>74786</t>
+          <t>75523</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>100933</t>
+          <t>100637</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>133563</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>49550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69984</t>
+          <t>68958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96813</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>193924</t>
+          <t>194460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224056</t>
+          <t>224590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>235693</t>
+          <t>237454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>269836</t>
+          <t>270075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>440444</t>
+          <t>440373</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>487060</t>
+          <t>485887</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45185</t>
+          <t>45901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>44128</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>57512</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>82234</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>49218</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69374</t>
+          <t>69332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3713,12 +3713,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61603</t>
+          <t>60443</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>97429</t>
+          <t>96936</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>124811</t>
+          <t>123731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40843</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58814</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>85673</t>
+          <t>86502</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>112986</t>
+          <t>114104</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -3904,12 +3904,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24543</t>
+          <t>22949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17939</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>36702</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23107</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>40166</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>19877</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>47502</t>
+          <t>47496</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>71919</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>93455</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>127291</t>
+          <t>126969</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>60185</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>37783</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>61352</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>85161</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>114276</t>
+          <t>115622</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5264,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>49383</t>
+          <t>49200</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>74625</t>
+          <t>73685</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>47907</t>
+          <t>48381</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>71428</t>
+          <t>71026</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>104408</t>
+          <t>102898</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>136767</t>
+          <t>137283</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>55608</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>80959</t>
+          <t>79100</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>66489</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>91984</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>127092</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>164695</t>
+          <t>163975</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>35282</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55723</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>73789</t>
+          <t>73523</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>104123</t>
+          <t>103759</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>205079</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>242558</t>
+          <t>241461</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>248719</t>
+          <t>246817</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>289592</t>
+          <t>286079</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>462588</t>
+          <t>464261</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>520195</t>
+          <t>519476</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5716,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>75851</t>
+          <t>75474</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>102495</t>
+          <t>104209</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>80469</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>109276</t>
+          <t>107518</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>162266</t>
+          <t>160970</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>202554</t>
+          <t>201467</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5942,12 +5942,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5957,39 +5957,39 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>4228</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7307,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>42177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55008</t>
+          <t>53784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>47356</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57930</t>
+          <t>58509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93240</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109937</t>
+          <t>109208</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>19453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>33133</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8215,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45118</t>
+          <t>44964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49856</t>
+          <t>50350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62043</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89574</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46138</t>
+          <t>46149</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41933</t>
+          <t>42370</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>64988</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75916</t>
+          <t>75831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103891</t>
+          <t>104836</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -8441,12 +8441,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24400</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41933</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>51449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58521</t>
+          <t>59722</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85197</t>
+          <t>85951</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179417</t>
+          <t>177664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209738</t>
+          <t>209673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>179238</t>
+          <t>180432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>213049</t>
+          <t>212242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>365845</t>
+          <t>364983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>411812</t>
+          <t>410670</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8667,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53737</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>51365</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>71179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98648</t>
+          <t>100304</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8815,12 +8815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9173,12 +9173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9208,12 +9208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58585</t>
+          <t>57577</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40285</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>59872</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>81989</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>109714</t>
+          <t>110174</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9434,12 +9434,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -9462,12 +9462,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>43178</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>91107</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>119399</t>
+          <t>119222</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -9575,12 +9575,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -9688,12 +9688,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>19831</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>22475</t>
+          <t>22003</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>39707</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -9801,12 +9801,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>39432</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -10027,12 +10027,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -10483,12 +10483,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>37986</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>59612</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>37561</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>60233</t>
+          <t>60086</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60399</t>
+          <t>61266</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>81955</t>
+          <t>80746</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>113458</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -10822,12 +10822,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>63877</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>64243</t>
+          <t>63095</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>89174</t>
+          <t>90278</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>121076</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>38007</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>59376</t>
+          <t>59313</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10950,12 +10950,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36868</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81610</t>
+          <t>81939</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>112701</t>
+          <t>113125</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -11048,12 +11048,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38685</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>60106</t>
+          <t>59733</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>58021</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>84057</t>
+          <t>83958</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>101234</t>
+          <t>102992</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>138062</t>
+          <t>136929</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -11161,12 +11161,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47013</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>55446</t>
+          <t>55675</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>67318</t>
+          <t>67451</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>96941</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -11274,12 +11274,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>186034</t>
+          <t>186309</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>223600</t>
+          <t>223754</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11289,12 +11289,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>193199</t>
+          <t>194001</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>232336</t>
+          <t>233070</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>391927</t>
+          <t>389253</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>446463</t>
+          <t>448126</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -11387,12 +11387,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>83462</t>
+          <t>81935</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>112011</t>
+          <t>109924</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11422,12 +11422,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>80537</t>
+          <t>81684</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>111353</t>
+          <t>109700</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>170845</t>
+          <t>169301</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>213014</t>
+          <t>212455</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -11500,12 +11500,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>22771</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -11613,12 +11613,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -12978,12 +12978,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>41444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33332</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69065</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82152</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -13091,12 +13091,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13106,12 +13106,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13126,12 +13126,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13161,12 +13161,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13176,12 +13176,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -13434,12 +13434,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13484,12 +13484,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13504,12 +13504,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44712</t>
+          <t>44502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66657</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -13886,12 +13886,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35169</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56106</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57807</t>
+          <t>58319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77461</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106712</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -13999,12 +13999,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69927</t>
+          <t>69463</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14034,12 +14034,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>47401</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70341</t>
+          <t>71218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14069,12 +14069,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>99993</t>
+          <t>100477</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>132350</t>
+          <t>131357</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>49928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54987</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14162,12 +14162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14182,12 +14182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69516</t>
+          <t>69897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96285</t>
+          <t>96524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>162071</t>
+          <t>162005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192756</t>
+          <t>194275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14240,12 +14240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14260,12 +14260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164765</t>
+          <t>165240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>197725</t>
+          <t>197839</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>334593</t>
+          <t>337663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>381173</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -14338,12 +14338,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14353,12 +14353,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14373,12 +14373,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>42295</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14408,12 +14408,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>52947</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>76631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -14451,12 +14451,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14466,12 +14466,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14486,12 +14486,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14501,12 +14501,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14521,12 +14521,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -14564,12 +14564,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14634,12 +14634,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14809,12 +14809,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14864,12 +14864,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -15020,12 +15020,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49426</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69865</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15035,12 +15035,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15055,12 +15055,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>58694</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78542</t>
+          <t>79009</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15090,12 +15090,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>113886</t>
+          <t>113169</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>141833</t>
+          <t>141969</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -15133,12 +15133,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>42775</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62637</t>
+          <t>62218</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15148,12 +15148,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52440</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15203,12 +15203,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>82227</t>
+          <t>82711</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>109237</t>
+          <t>109032</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -15246,12 +15246,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15374,12 +15374,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15394,12 +15394,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15409,12 +15409,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23226</t>
+          <t>23405</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -15472,12 +15472,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15487,12 +15487,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15522,12 +15522,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15542,12 +15542,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -15585,12 +15585,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15600,12 +15600,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15620,12 +15620,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15655,12 +15655,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -15698,12 +15698,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15713,12 +15713,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15733,12 +15733,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>515</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15768,12 +15768,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -16154,12 +16154,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32959</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -16169,12 +16169,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -16189,12 +16189,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -16380,12 +16380,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>48526</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -16395,12 +16395,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -16415,12 +16415,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>80081</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -16430,12 +16430,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -16450,12 +16450,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>108317</t>
+          <t>110543</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>143988</t>
+          <t>145571</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -16465,12 +16465,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -16493,12 +16493,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41532</t>
+          <t>41854</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>64273</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -16528,12 +16528,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>33055</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>53703</t>
+          <t>53859</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -16543,12 +16543,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -16563,12 +16563,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>81390</t>
+          <t>80277</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>112977</t>
+          <t>112178</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -16578,12 +16578,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -16606,12 +16606,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>66473</t>
+          <t>66369</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16621,12 +16621,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16641,12 +16641,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>54948</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>79635</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16676,12 +16676,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>105851</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>139202</t>
+          <t>138249</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16691,12 +16691,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -16719,12 +16719,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62486</t>
+          <t>60880</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>88256</t>
+          <t>87327</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16734,12 +16734,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16754,12 +16754,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>62035</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>88638</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16769,12 +16769,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>131190</t>
+          <t>128673</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>166821</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16804,12 +16804,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -16832,12 +16832,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>34111</t>
+          <t>34530</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>53915</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16847,12 +16847,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16867,12 +16867,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>60439</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>78212</t>
+          <t>77895</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>108737</t>
+          <t>105800</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>165780</t>
+          <t>167654</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>200632</t>
+          <t>202847</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>172534</t>
+          <t>174018</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>209762</t>
+          <t>211688</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>349752</t>
+          <t>350723</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>402514</t>
+          <t>404009</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>83885</t>
+          <t>85656</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>61108</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>87994</t>
+          <t>86814</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>128516</t>
+          <t>125951</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>165392</t>
+          <t>163706</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>39448</t>
+          <t>40129</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -17339,42 +17339,42 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>4609</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>9332</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
         </is>
       </c>
     </row>
